--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,95; 66,13</t>
+          <t>59,57; 65,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,33; 78,14</t>
+          <t>72,58; 78,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,89; 72,46</t>
+          <t>65,83; 72,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,6; 58,15</t>
+          <t>49,8; 58,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,49; 78,21</t>
+          <t>73,27; 77,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,63; 87,51</t>
+          <t>83,62; 87,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,62; 86,16</t>
+          <t>81,47; 86,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,13; 66,34</t>
+          <t>61,0; 66,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,25; 72,11</t>
+          <t>68,25; 72,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,71; 82,97</t>
+          <t>79,75; 82,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,7; 79,72</t>
+          <t>75,66; 79,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,66; 62,3</t>
+          <t>57,57; 62,16</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,06</t>
+          <t>33,11; 37,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,12; 47,6</t>
+          <t>42,79; 47,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,42; 47,63</t>
+          <t>43,2; 47,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 32,41</t>
+          <t>19,5; 32,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,05; 52,92</t>
+          <t>48,06; 53,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,3; 60,14</t>
+          <t>55,42; 60,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,87; 56,35</t>
+          <t>51,76; 56,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 56,62</t>
+          <t>32,26; 54,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,7; 44,3</t>
+          <t>40,99; 44,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,41; 52,75</t>
+          <t>49,61; 52,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,12; 51,25</t>
+          <t>48,04; 51,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 43,52</t>
+          <t>28,49; 43,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 41,75</t>
+          <t>33,24; 42,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,77; 50,59</t>
+          <t>40,3; 50,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,54; 43,15</t>
+          <t>34,91; 43,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,46; 32,13</t>
+          <t>24,55; 32,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,44; 54,95</t>
+          <t>45,96; 54,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,15; 56,81</t>
+          <t>47,28; 56,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,06; 50,96</t>
+          <t>42,34; 51,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,71; 33,22</t>
+          <t>27,16; 33,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,27; 46,86</t>
+          <t>40,33; 46,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,16; 52,13</t>
+          <t>45,39; 52,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,95; 45,93</t>
+          <t>39,95; 46,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,75; 31,5</t>
+          <t>26,82; 31,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,34</t>
+          <t>42,58; 46,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,0; 55,43</t>
+          <t>52,25; 55,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,12; 51,46</t>
+          <t>48,02; 51,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 35,22</t>
+          <t>25,34; 35,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,74; 62,17</t>
+          <t>58,8; 62,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,83; 69,04</t>
+          <t>65,94; 69,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,68; 63,05</t>
+          <t>59,76; 63,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,49; 53,28</t>
+          <t>38,54; 53,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 53,79</t>
+          <t>51,26; 53,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,59; 62,06</t>
+          <t>59,64; 61,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,45; 56,93</t>
+          <t>54,61; 56,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,84; 43,36</t>
+          <t>33,94; 42,88</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>618505; 682290</t>
+          <t>614604; 676515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>704918; 761630</t>
+          <t>707371; 761539</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>497071; 546601</t>
+          <t>496596; 546789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>255418; 299445</t>
+          <t>256446; 300257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>966529; 1028598</t>
+          <t>963631; 1025056</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1118826; 1170695</t>
+          <t>1118731; 1172441</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>811824; 856990</t>
+          <t>810372; 858259</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>461850; 501213</t>
+          <t>460870; 501759</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1601758; 1692406</t>
+          <t>1601808; 1691276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1843273; 1918691</t>
+          <t>1844269; 1919074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1323912; 1394322</t>
+          <t>1323351; 1395906</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>732546; 791548</t>
+          <t>731421; 789749</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>562139; 644454</t>
+          <t>560680; 639006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>846920; 934917</t>
+          <t>840404; 933256</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>901657; 989034</t>
+          <t>897028; 990808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>454661; 742277</t>
+          <t>446681; 736898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>762825; 840127</t>
+          <t>763045; 843641</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>972088; 1057069</t>
+          <t>974095; 1058863</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1031359; 1120392</t>
+          <t>1029205; 1121418</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>723050; 1267091</t>
+          <t>722027; 1211469</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1335469; 1453407</t>
+          <t>1344811; 1455783</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1838830; 1963113</t>
+          <t>1846315; 1962254</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1955855; 2083115</t>
+          <t>1952708; 2085194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1315341; 1970595</t>
+          <t>1290098; 1968378</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>184355; 230200</t>
+          <t>183309; 231634</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>196195; 243438</t>
+          <t>193918; 242613</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188873; 235969</t>
+          <t>190909; 239126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158163; 207765</t>
+          <t>158727; 208603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>216502; 261768</t>
+          <t>218972; 261814</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>216246; 260526</t>
+          <t>216822; 261272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>230976; 279840</t>
+          <t>232488; 281243</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>176424; 219385</t>
+          <t>179386; 221097</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>413948; 481628</t>
+          <t>414535; 478275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>424413; 489958</t>
+          <t>426572; 488743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>437872; 503417</t>
+          <t>437860; 504420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>349655; 411754</t>
+          <t>350541; 415282</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1395018; 1518207</t>
+          <t>1395138; 1511228</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1778158; 1895592</t>
+          <t>1786726; 1904001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1625187; 1738202</t>
+          <t>1621770; 1739547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>842040; 1215615</t>
+          <t>874697; 1210115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1984896; 2100982</t>
+          <t>1987034; 2098254</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2339685; 2453726</t>
+          <t>2343503; 2455327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2107943; 2226847</t>
+          <t>2110727; 2230096</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1406286; 1946674</t>
+          <t>1408107; 1964442</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3412677; 3580049</t>
+          <t>3411780; 3578155</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4155919; 4327726</t>
+          <t>4159327; 4319456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3762017; 3933488</t>
+          <t>3773653; 3936288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2404899; 3080944</t>
+          <t>2411425; 3046895</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>57,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,57; 65,57</t>
+          <t>59,56; 65,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,58; 78,14</t>
+          <t>72,8; 78,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 72,49</t>
+          <t>65,93; 72,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,8; 58,31</t>
+          <t>46,26; 54,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,27; 77,94</t>
+          <t>73,42; 78,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,62; 87,64</t>
+          <t>83,66; 87,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,47; 86,29</t>
+          <t>81,75; 86,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,0; 66,41</t>
+          <t>60,18; 65,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,25; 72,07</t>
+          <t>68,19; 72,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,75; 82,99</t>
+          <t>79,68; 83,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,66; 79,81</t>
+          <t>75,64; 79,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,57; 62,16</t>
+          <t>55,64; 60,33</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,11; 37,73</t>
+          <t>33,27; 37,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,79; 47,52</t>
+          <t>42,96; 47,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,2; 47,72</t>
+          <t>43,4; 47,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 32,17</t>
+          <t>28,33; 32,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,06; 53,14</t>
+          <t>47,84; 53,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,42; 60,24</t>
+          <t>55,39; 60,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,76; 56,4</t>
+          <t>51,82; 56,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,26; 54,14</t>
+          <t>32,32; 36,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,99; 44,37</t>
+          <t>40,81; 44,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,61; 52,72</t>
+          <t>49,42; 52,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,04; 51,3</t>
+          <t>48,03; 51,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,49; 43,47</t>
+          <t>30,78; 33,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,24; 42,01</t>
+          <t>33,34; 41,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,3; 50,42</t>
+          <t>40,9; 50,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,73</t>
+          <t>34,83; 43,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,55; 32,26</t>
+          <t>23,93; 31,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,96; 54,96</t>
+          <t>45,21; 54,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,28; 56,97</t>
+          <t>46,54; 56,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,34; 51,22</t>
+          <t>42,51; 51,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 33,48</t>
+          <t>26,92; 32,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,33; 46,53</t>
+          <t>40,24; 46,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,39; 52,0</t>
+          <t>45,6; 52,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,95; 46,02</t>
+          <t>39,84; 46,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,82; 31,77</t>
+          <t>26,11; 30,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,58; 46,12</t>
+          <t>42,75; 46,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,25; 55,68</t>
+          <t>52,05; 55,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,02; 51,5</t>
+          <t>48,01; 51,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,06</t>
+          <t>31,23; 34,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,8; 62,09</t>
+          <t>58,68; 61,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,94; 69,08</t>
+          <t>65,9; 69,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,76; 63,14</t>
+          <t>59,76; 63,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,54; 53,76</t>
+          <t>38,33; 41,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,26; 53,76</t>
+          <t>51,31; 53,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,64; 61,94</t>
+          <t>59,53; 62,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,61; 56,97</t>
+          <t>54,53; 56,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 42,88</t>
+          <t>35,32; 37,53</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276915</t>
+          <t>291268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>482580</t>
+          <t>517509</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>759495</t>
+          <t>808777</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>614604; 676515</t>
+          <t>614546; 678009</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>707371; 761539</t>
+          <t>709581; 761744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>496596; 546789</t>
+          <t>497320; 548893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>256446; 300257</t>
+          <t>267601; 315611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>963631; 1025056</t>
+          <t>965566; 1027390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1118731; 1172441</t>
+          <t>1119187; 1171165</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>810372; 858259</t>
+          <t>813142; 858815</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>460870; 501759</t>
+          <t>494684; 538462</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1601808; 1691276</t>
+          <t>1600211; 1691984</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1844269; 1919074</t>
+          <t>1842590; 1921346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1323351; 1395906</t>
+          <t>1322971; 1392424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>731421; 789749</t>
+          <t>779241; 844961</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>645229</t>
+          <t>675345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>880361</t>
+          <t>743212</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1525590</t>
+          <t>1418558</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>560680; 639006</t>
+          <t>563378; 642493</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>840404; 933256</t>
+          <t>843688; 932945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>897028; 990808</t>
+          <t>901156; 993141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>446681; 736898</t>
+          <t>632015; 726744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>763045; 843641</t>
+          <t>759604; 842094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>974095; 1058863</t>
+          <t>973732; 1060167</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1029205; 1121418</t>
+          <t>1030371; 1122327</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>722027; 1211469</t>
+          <t>701728; 785754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1344811; 1455783</t>
+          <t>1339130; 1458441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1846315; 1962254</t>
+          <t>1839324; 1959956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1952708; 2085194</t>
+          <t>1952432; 2082563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1290098; 1968378</t>
+          <t>1354808; 1480076</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181938</t>
+          <t>194718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>199190</t>
+          <t>220042</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>381128</t>
+          <t>414760</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>183309; 231634</t>
+          <t>183833; 230094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193918; 242613</t>
+          <t>196821; 244229</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190909; 239126</t>
+          <t>190455; 236334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158727; 208603</t>
+          <t>170272; 221123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>218972; 261814</t>
+          <t>215387; 260637</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>216822; 261272</t>
+          <t>213450; 259939</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>232488; 281243</t>
+          <t>233438; 280837</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>179386; 221097</t>
+          <t>197801; 240937</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>414535; 478275</t>
+          <t>413610; 479320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>426572; 488743</t>
+          <t>428533; 491030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>437860; 504420</t>
+          <t>436654; 508547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>350541; 415282</t>
+          <t>377706; 446306</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1104081</t>
+          <t>1161332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1562131</t>
+          <t>1480763</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2666213</t>
+          <t>2642096</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1395138; 1511228</t>
+          <t>1400719; 1511926</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1786726; 1904001</t>
+          <t>1779835; 1900380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1621770; 1739547</t>
+          <t>1621533; 1738844</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>874697; 1210115</t>
+          <t>1099569; 1219351</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1987034; 2098254</t>
+          <t>1983020; 2093417</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2343503; 2455327</t>
+          <t>2342277; 2459816</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2110727; 2230096</t>
+          <t>2110791; 2232839</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1408107; 1964442</t>
+          <t>1428908; 1533032</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3411780; 3578155</t>
+          <t>3414949; 3578136</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4159327; 4319456</t>
+          <t>4151724; 4324876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3773653; 3936288</t>
+          <t>3767552; 3930684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2411425; 3046895</t>
+          <t>2560371; 2720350</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
